--- a/Sensitivity_PSNR_Woman.xlsx
+++ b/Sensitivity_PSNR_Woman.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D980A910-C17B-4C61-996D-446D5071C600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F1D38D0-1E53-488E-8927-62D662A384AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{64D9CFC5-8141-4F6F-A4D0-17AB56AC0941}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3702E400-C4AA-47A6-B36A-CF5D31397F13}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -442,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8221B15-AA60-496D-AED7-D07E04EC6F6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD3ABAF-EF9E-4F61-9EBE-1C0072D1AF1C}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -576,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCAF7CA8-9FCC-493B-B4B7-A9E191EEE07A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F045C6D8-965A-499B-8435-D9416C878ABE}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -585,7 +588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F27C7E-53A2-45E7-B237-9166F4DD1A31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A4AF9CF-ED68-45D5-8442-68B4C05DF76E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
